--- a/StructureDefinition-inera-ehds-lm-vaccination-history.xlsx
+++ b/StructureDefinition-inera-ehds-lm-vaccination-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T07:52:35+00:00</t>
+    <t>2026-09-30T09:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-lm-vaccination-history.xlsx
+++ b/StructureDefinition-inera-ehds-lm-vaccination-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:02:48+00:00</t>
+    <t>2026-09-30T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-lm-vaccination-history.xlsx
+++ b/StructureDefinition-inera-ehds-lm-vaccination-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T10:52:57+00:00</t>
+    <t>2026-10-01T18:35:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-inera-ehds-lm-vaccination-history.xlsx
+++ b/StructureDefinition-inera-ehds-lm-vaccination-history.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T18:35:17+00:00</t>
+    <t>2026-10-02T11:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
